--- a/ig/DM_FINESS_New/ValueSet-jdv-rcp-organe-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-rcp-organe-cisis.xlsx
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250606103858</t>
+    <t>20250616134740</t>
   </si>
   <si>
     <t>Name</t>
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-06T10:38:58+01:00</t>
+    <t>2025-06-16T13:47:40+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-jdv-rcp-organe-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-rcp-organe-cisis.xlsx
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250616134740</t>
+    <t>20250624152101</t>
   </si>
   <si>
     <t>Name</t>
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-16T13:47:40+01:00</t>
+    <t>2025-06-24T15:21:01+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-jdv-rcp-organe-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-rcp-organe-cisis.xlsx
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250624152101</t>
+    <t>20251216141840</t>
   </si>
   <si>
     <t>Name</t>
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24T15:21:01+01:00</t>
+    <t>2025-12-16T14:18:40+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -108,7 +108,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/terminologie-cim-10</t>
+    <t>http://hl7.org/fhir/sid/icd-10</t>
   </si>
   <si>
     <t>C3211</t>
@@ -186,7 +186,7 @@
     <t>C94529</t>
   </si>
   <si>
-    <t>Vulve et vagin</t>
+    <t>région vulvo-vaginale</t>
   </si>
   <si>
     <t>C12664</t>
@@ -195,7 +195,7 @@
     <t>Péritoine-rétropéritoine</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/terminologie-ncit</t>
+    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl</t>
   </si>
   <si>
     <t>MED-237</t>
@@ -222,13 +222,13 @@
     <t>57171008</t>
   </si>
   <si>
-    <t>structure du système hématopoïétique</t>
+    <t>système hématopoïétique</t>
   </si>
   <si>
     <t>119253004</t>
   </si>
   <si>
-    <t>voie aérodigestive supérieure</t>
+    <t>voies aérodigestives supérieures</t>
   </si>
   <si>
     <t>303270005</t>
@@ -294,7 +294,7 @@
     <t>48477009</t>
   </si>
   <si>
-    <t>lèvre de la bouche</t>
+    <t>lèvre</t>
   </si>
   <si>
     <t>21974007</t>
@@ -423,10 +423,10 @@
     <t>nerf périphérique</t>
   </si>
   <si>
-    <t>1290040004</t>
-  </si>
-  <si>
-    <t>œil entier</t>
+    <t>81745001</t>
+  </si>
+  <si>
+    <t>œil</t>
   </si>
   <si>
     <t>387910009</t>
@@ -438,13 +438,13 @@
     <t>23451007</t>
   </si>
   <si>
-    <t>glande surrénale</t>
+    <t>glande suprarénale</t>
   </si>
   <si>
     <t>69748006</t>
   </si>
   <si>
-    <t>glande thyroïde</t>
+    <t>thyroïde</t>
   </si>
   <si>
     <t>72410000</t>

--- a/ig/DM_FINESS_New/ValueSet-jdv-rcp-organe-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-rcp-organe-cisis.xlsx
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251216141840</t>
+    <t>20260220142105</t>
   </si>
   <si>
     <t>Name</t>
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T14:18:40+01:00</t>
+    <t>2026-02-20T14:21:05+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,12 +96,84 @@
     <t>Concept</t>
   </si>
   <si>
+    <t>C85</t>
+  </si>
+  <si>
+    <t>Lymphome non hodgkinien, de types autres et non précisés</t>
+  </si>
+  <si>
     <t>C88</t>
   </si>
   <si>
     <t>Maladies immunoprolifératives malignes</t>
   </si>
   <si>
+    <t>C81</t>
+  </si>
+  <si>
+    <t>Lymphome de Hodgkin</t>
+  </si>
+  <si>
+    <t>C95.1</t>
+  </si>
+  <si>
+    <t>Leucémie chronique à cellules non précisées</t>
+  </si>
+  <si>
+    <t>C91.1</t>
+  </si>
+  <si>
+    <t>Leucémie lymphoïde chronique à cellules B</t>
+  </si>
+  <si>
+    <t>C91.0</t>
+  </si>
+  <si>
+    <t>Leucémie lymphoblastique aigüe [LLA]</t>
+  </si>
+  <si>
+    <t>C92</t>
+  </si>
+  <si>
+    <t>Leucémie myéloïde</t>
+  </si>
+  <si>
+    <t>C92.0</t>
+  </si>
+  <si>
+    <t>Leucémie myéloblastique aigüe [LAM]</t>
+  </si>
+  <si>
+    <t>C92.1</t>
+  </si>
+  <si>
+    <t>Leucémie myéloïde chronique [LMC] ABL-BCR positif</t>
+  </si>
+  <si>
+    <t>C93.0</t>
+  </si>
+  <si>
+    <t>Leucémie monoblastique/monocytaire aigüe</t>
+  </si>
+  <si>
+    <t>C95.0</t>
+  </si>
+  <si>
+    <t>Leucémie aiguë à cellules non précisées</t>
+  </si>
+  <si>
+    <t>C94.6</t>
+  </si>
+  <si>
+    <t>Maladie myélodysplasique et myéloproliférative, non classée ailleurs</t>
+  </si>
+  <si>
+    <t>C90.0</t>
+  </si>
+  <si>
+    <t>Myélome multiple</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -109,78 +181,6 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/sid/icd-10</t>
-  </si>
-  <si>
-    <t>C3211</t>
-  </si>
-  <si>
-    <t>lymphome non hodgkinien</t>
-  </si>
-  <si>
-    <t>C9357</t>
-  </si>
-  <si>
-    <t>Lymphome de Hodgkin</t>
-  </si>
-  <si>
-    <t>C3483</t>
-  </si>
-  <si>
-    <t>leucémie chronique</t>
-  </si>
-  <si>
-    <t>C3163</t>
-  </si>
-  <si>
-    <t>Leucémie lymphocytique chronique</t>
-  </si>
-  <si>
-    <t>C3167</t>
-  </si>
-  <si>
-    <t>Leucémie lymphoblastique aiguë</t>
-  </si>
-  <si>
-    <t>C3172</t>
-  </si>
-  <si>
-    <t>Leucémie myéloïde</t>
-  </si>
-  <si>
-    <t>C3171</t>
-  </si>
-  <si>
-    <t>leucémie myéloïde aiguë</t>
-  </si>
-  <si>
-    <t>C3174</t>
-  </si>
-  <si>
-    <t>leucémie myéloïde chronique BCR-ABL positive</t>
-  </si>
-  <si>
-    <t>C4861</t>
-  </si>
-  <si>
-    <t>leucémie monocytaire aiguë</t>
-  </si>
-  <si>
-    <t>C9300</t>
-  </si>
-  <si>
-    <t>leucémie aiguë</t>
-  </si>
-  <si>
-    <t>C27262</t>
-  </si>
-  <si>
-    <t>maladies myélodysplasiques-myéloprolifératives</t>
-  </si>
-  <si>
-    <t>C3242</t>
-  </si>
-  <si>
-    <t>myélome à cellules plasmatiques</t>
   </si>
   <si>
     <t>C94529</t>
@@ -709,7 +709,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -737,15 +737,111 @@
         <v>28</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -755,7 +851,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -772,129 +868,33 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>32</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>34</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>36</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="B17" t="s" s="2">
         <v>59</v>
       </c>
     </row>
@@ -946,15 +946,15 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>28</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="B6" t="s" s="2">
         <v>66</v>
@@ -1296,15 +1296,15 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>28</v>
+        <v>52</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>145</v>

--- a/ig/DM_FINESS_New/ValueSet-jdv-rcp-organe-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-rcp-organe-cisis.xlsx
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260220142105</t>
+    <t>20260311144904</t>
   </si>
   <si>
     <t>Name</t>
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-20T14:21:05+01:00</t>
+    <t>2026-03-11T14:49:04+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-jdv-rcp-organe-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-rcp-organe-cisis.xlsx
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260311144904</t>
+    <t>20260420150251</t>
   </si>
   <si>
     <t>Name</t>
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T14:49:04+01:00</t>
+    <t>2026-04-20T15:02:51+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
